--- a/erp-server/erp-server-wms/src/main/resources/excel/inventory.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/inventory.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <r>
       <rPr>
@@ -108,6 +108,9 @@
     <t>仓库名称</t>
   </si>
   <si>
+    <t>仓位名称</t>
+  </si>
+  <si>
     <t>实际库存</t>
   </si>
   <si>
@@ -123,12 +126,6 @@
     <t>待检库存</t>
   </si>
   <si>
-    <t>金蝶库存</t>
-  </si>
-  <si>
-    <t>库存差异</t>
-  </si>
-  <si>
     <t>{.skuNo}</t>
   </si>
   <si>
@@ -147,6 +144,9 @@
     <t>{.warehouseName}</t>
   </si>
   <si>
+    <t>{.warehouseLocationName}</t>
+  </si>
+  <si>
     <t>{.realQty}</t>
   </si>
   <si>
@@ -160,12 +160,6 @@
   </si>
   <si>
     <t>{.waitqcQty}</t>
-  </si>
-  <si>
-    <t>{.kingdeeQty}</t>
-  </si>
-  <si>
-    <t>{.diffQty}</t>
   </si>
 </sst>
 </file>
@@ -1128,7 +1122,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.875" customWidth="1"/>
@@ -1137,16 +1131,14 @@
     <col min="4" max="4" width="21.375" customWidth="1"/>
     <col min="5" max="5" width="14.125" customWidth="1"/>
     <col min="6" max="6" width="21.25" customWidth="1"/>
-    <col min="7" max="7" width="14.5" customWidth="1"/>
-    <col min="8" max="8" width="14.75" customWidth="1"/>
-    <col min="9" max="9" width="12.625" customWidth="1"/>
-    <col min="10" max="10" width="12.875" customWidth="1"/>
-    <col min="11" max="11" width="14.625" customWidth="1"/>
-    <col min="12" max="12" width="12.125" customWidth="1"/>
-    <col min="13" max="13" width="13.625" customWidth="1"/>
+    <col min="7" max="8" width="14.5" customWidth="1"/>
+    <col min="9" max="9" width="14.75" customWidth="1"/>
+    <col min="10" max="10" width="12.625" customWidth="1"/>
+    <col min="11" max="11" width="12.875" customWidth="1"/>
+    <col min="12" max="12" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="17.25" spans="1:13">
+    <row r="1" s="1" customFormat="1" ht="17.25" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1183,49 +1175,43 @@
       <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>19</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>20</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>21</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>22</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>23</v>
-      </c>
-      <c r="L2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-wms/src/main/resources/excel/inventory.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/inventory.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <r>
       <rPr>
@@ -108,9 +108,6 @@
     <t>仓库名称</t>
   </si>
   <si>
-    <t>仓位名称</t>
-  </si>
-  <si>
     <t>实际库存</t>
   </si>
   <si>
@@ -142,9 +139,6 @@
   </si>
   <si>
     <t>{.warehouseName}</t>
-  </si>
-  <si>
-    <t>{.warehouseLocationName}</t>
   </si>
   <si>
     <t>{.realQty}</t>
@@ -1122,7 +1116,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.875" customWidth="1"/>
@@ -1131,14 +1125,14 @@
     <col min="4" max="4" width="21.375" customWidth="1"/>
     <col min="5" max="5" width="14.125" customWidth="1"/>
     <col min="6" max="6" width="21.25" customWidth="1"/>
-    <col min="7" max="8" width="14.5" customWidth="1"/>
-    <col min="9" max="9" width="14.75" customWidth="1"/>
-    <col min="10" max="10" width="12.625" customWidth="1"/>
-    <col min="11" max="11" width="12.875" customWidth="1"/>
-    <col min="12" max="12" width="14.625" customWidth="1"/>
+    <col min="7" max="7" width="14.5" customWidth="1"/>
+    <col min="8" max="8" width="14.75" customWidth="1"/>
+    <col min="9" max="9" width="12.625" customWidth="1"/>
+    <col min="10" max="10" width="12.875" customWidth="1"/>
+    <col min="11" max="11" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="17.25" spans="1:12">
+    <row r="1" s="1" customFormat="1" ht="17.25" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1172,46 +1166,40 @@
       <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>18</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>19</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>20</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>21</v>
-      </c>
-      <c r="K2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
